--- a/Test1.xlsx
+++ b/Test1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\OneDrive\Bureaublad\PTRA GAME\PRTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FA06C23-4ECF-4E2B-A650-3AA776745691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17DB950-AE10-43C0-8750-3D18163E3AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B210B30-21CF-4559-A670-8C55096C93B6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Datum</t>
   </si>
@@ -207,6 +207,15 @@
   </si>
   <si>
     <t>Game zou moeten sluiten (Consol logt "QUIT!")</t>
+  </si>
+  <si>
+    <t>Afval Generator</t>
+  </si>
+  <si>
+    <t>Begin te spel te spelen</t>
+  </si>
+  <si>
+    <t>Er zou afval in de game moeten zitten overal in de map</t>
   </si>
 </sst>
 </file>
@@ -815,6 +824,15 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>

--- a/Test1.xlsx
+++ b/Test1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\OneDrive\Bureaublad\PTRA GAME\PRTA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jarno\Documents\GitHub\PRTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17DB950-AE10-43C0-8750-3D18163E3AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE47D71-8DD2-4AF9-A84B-6445393B3073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B210B30-21CF-4559-A670-8C55096C93B6}"/>
+    <workbookView xWindow="1815" yWindow="-15870" windowWidth="25440" windowHeight="15270" xr2:uid="{8B210B30-21CF-4559-A670-8C55096C93B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>Datum</t>
   </si>
@@ -216,6 +216,18 @@
   </si>
   <si>
     <t>Er zou afval in de game moeten zitten overal in de map</t>
+  </si>
+  <si>
+    <t>Healthbar</t>
+  </si>
+  <si>
+    <t>Tegen iets gevaarlijks aanlopen</t>
+  </si>
+  <si>
+    <t>Het moet leeglopen als je tegen een gevaarlijk object loopt.</t>
+  </si>
+  <si>
+    <t>Ja</t>
   </si>
 </sst>
 </file>
@@ -262,7 +274,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -278,7 +290,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -810,7 +822,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" t="s">
         <v>52</v>
@@ -822,7 +834,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" t="s">
         <v>56</v>
@@ -834,28 +846,40 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
     </row>
   </sheetData>
